--- a/XLSX/LoIN_08_ŠVOK.V_VVK2_NSIK_s2.xlsx
+++ b/XLSX/LoIN_08_ŠVOK.V_VVK2_NSIK_s2.xlsx
@@ -183,7 +183,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,15 +207,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -668,27 +672,127 @@
     <row r="2" ht="127" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Funkcinės sistemos kodas - ClassificationSystem.NSIK LF arba „NSIK LF“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Funkcinės sistemos kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLF</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LF</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Techninės sistemos kodas - ClassificationSystem.NSIK LT arba „NSIK LT“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Techninės sistemos kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLT</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LT</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Komponento kodas - ClassificationSystemNSIK LK arba „NSIK LK“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Komponento kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLK</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LK</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Erdvės kodas - ClassificationSystem.NSIK B arba „NSIK B“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Erdvės kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeB</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK B</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Statinio kodas - ClassificationSystem.NSIK E arba „NSIK E“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Statinio kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeE</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK E</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -747,493 +851,469 @@
     <row r="4" outlineLevel="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Mechaninis reguliatorius</t>
+          <t>Apsauginė sankaba</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>HF</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>FNA</t>
         </is>
       </c>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Sklendė sklendė</t>
+          <t>Geometrinis koordinavimo elementas</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Mechaninis signalinis komponentas, reguliuojantis oro ar skysčio srautą.</t>
+          <t>Komponentas, apsaugantis nuo mechaninės jėgos, atjungiantis perdavimo mechanizmą, kai sukimo momentas viršija ribinę reikšmę.</t>
         </is>
       </c>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="9" t="n"/>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="9" t="n"/>
-      <c r="R4" s="9" t="n"/>
-      <c r="S4" s="9" t="n"/>
-      <c r="T4" s="10" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="5" outlineLevel="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="T5" s="12" t="n"/>
+      <c r="A5" s="12" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T5" s="14" t="n"/>
     </row>
     <row r="6" outlineLevel="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="12" t="n"/>
+      <c r="T6" s="14" t="n"/>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mechaninis reguliatorius</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>KJA</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Sklendė</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Mechaninis signalinis komponentas, reguliuojantis oro ar skysčio srautą.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="12" t="n"/>
+      <c r="T8" s="14" t="n"/>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Priešgaisrinė sklendė</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>FMA</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Priešgaisrinė sklendė</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Apsauginis komponentas, gaisro atveju uždarantis oro srautą.</t>
         </is>
       </c>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="T7" s="12" t="n"/>
-    </row>
-    <row r="8" outlineLevel="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="12" t="n"/>
+      <c r="T10" s="14" t="n"/>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Priešgaisrinė ir dūmų sklendė</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>FMC</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Priešgaisrinė ir dūmų sklendė</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Apsauginis komponentas, uždarantis oro srautą dūmų ir (ar) gaisro aptikimo atveju.</t>
         </is>
       </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="10" t="inlineStr">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="T9" s="12" t="n"/>
-    </row>
-    <row r="10" outlineLevel="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="12" t="n"/>
+      <c r="T12" s="14" t="n"/>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Šilumos siurblys</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>EGA</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Šaldymo mašina</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Šiluminės energijos transformavimo įrenginys galintis gaminti šilumą ir (arba) vėsą, dirbantis Karno / garo kompresijos ciklo / absorbcijos principais.</t>
         </is>
       </c>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="10" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="T11" s="12" t="n"/>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="12" t="n"/>
+      <c r="T14" s="14" t="n"/>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Izoliacija</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>RQA</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Izoliacija</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Vietinį klimatą stabilizuojantis komponentas ribojant šilumos ar garso perdavimą.</t>
         </is>
       </c>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="9" t="n"/>
-      <c r="T12" s="10" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="T13" s="12" t="n"/>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Priešgaisrinė izoliacija</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>FMH</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Priešgaisrinė izoliacija</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Apsauginis komponentas, izoliuojantis paviršių nuo ugnies.</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="9" t="n"/>
-      <c r="S14" s="9" t="n"/>
-      <c r="T14" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="T15" s="12" t="n"/>
-    </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Ortakis</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>WPB</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Ortakis</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Apskritos arba kampuotos standaus skerspjūvio formos komponentas, uždaroje aplinkoje nukreipiantis oro ir (arba) dujų srautą.</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="9" t="n"/>
-      <c r="T16" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T16" s="14" t="n"/>
     </row>
     <row r="17" outlineLevel="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="T17" s="12" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Thickness</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>The geometric thickness of the object.</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T17" s="14" t="n"/>
     </row>
     <row r="18" outlineLevel="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Išardoma jungtis</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>XMA</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Išardoma jungtis</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Išardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
-      <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="9" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>Pset_QuantityTakeOff.Area</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>Calculated area for the object.</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="n"/>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="T19" s="12" t="n"/>
+      <c r="A19" s="12" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T19" s="14" t="n"/>
     </row>
     <row r="20" outlineLevel="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Neišardoma jungtis</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>XMB</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Neišardoma jungtis</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Neišardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
-      <c r="O20" s="9" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="9" t="n"/>
-      <c r="S20" s="9" t="n"/>
-      <c r="T20" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T20" s="14" t="n"/>
     </row>
     <row r="21" outlineLevel="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="T21" s="12" t="n"/>
+      <c r="A21" s="12" t="n"/>
+      <c r="T21" s="14" t="n"/>
     </row>
     <row r="22" outlineLevel="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Kampinė jungtis</t>
+          <t>Priešgaisrinė izoliacija</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1248,208 +1328,164 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>XMD</t>
+          <t>FMH</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Kampinė jungtis</t>
+          <t>Priešgaisrinė izoliacija</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Komponentas, skirtas sujungti ir pakeisti fluido srauto kryptį.</t>
+          <t>Apsauginis komponentas, izoliuojantis paviršių nuo ugnies.</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="9" t="n"/>
-      <c r="T22" s="10" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="23" outlineLevel="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="T23" s="12" t="n"/>
+      <c r="A23" s="12" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.FireRating</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>Fire rating for this object. It is given according to the national fire safety classification.</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T23" s="14" t="n"/>
     </row>
     <row r="24" outlineLevel="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Grotelės</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>NAC</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Grotelės</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Užpildantis komponentas, praleidžiantis skysčius.</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9" t="n"/>
-      <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="9" t="n"/>
-      <c r="S24" s="9" t="n"/>
-      <c r="T24" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P24" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T24" s="14" t="n"/>
     </row>
     <row r="25" outlineLevel="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="T25" s="12" t="n"/>
+      <c r="A25" s="12" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Thickness</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>The geometric thickness of the object.</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T25" s="14" t="n"/>
     </row>
     <row r="26" outlineLevel="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Difuzorius</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>RND</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Difuzorius</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Srauto ribotuvas, fiksuotomis priemonėmis apribojantis ir formuojantis srautą.</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="9" t="n"/>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="9" t="n"/>
-      <c r="S26" s="9" t="n"/>
-      <c r="T26" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>Pset_QuantityTakeOff.Area</t>
+        </is>
+      </c>
+      <c r="N26" s="13" t="inlineStr">
+        <is>
+          <t>Calculated area for the object.</t>
+        </is>
+      </c>
+      <c r="P26" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T26" s="14" t="n"/>
     </row>
     <row r="27" outlineLevel="1">
-      <c r="A27" s="11" t="n"/>
-      <c r="T27" s="12" t="n"/>
+      <c r="A27" s="12" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T27" s="14" t="n"/>
     </row>
     <row r="28" outlineLevel="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Oro skirstytuvas</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>HF</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>%RND10</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Oro skirstytuvas</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Oro srautą formuojantis, praleidžiantis ir maišantis įrenginys.</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="9" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="10" t="inlineStr">
-        <is>
-          <t>ŠVOK.V</t>
-        </is>
-      </c>
+      <c r="A28" s="12" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N28" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T28" s="14" t="n"/>
     </row>
     <row r="29" outlineLevel="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="T29" s="12" t="n"/>
+      <c r="A29" s="12" t="n"/>
+      <c r="T29" s="14" t="n"/>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Dujų reguliavimo vožtuvas</t>
+          <t>Ortakis</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1464,46 +1500,55 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>QNB</t>
+          <t>WPB</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Reguliavimo sklendė</t>
+          <t>Ortakis</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Komponentas, sandariose skysčio sistemose reguliuojantis dujų srautą.</t>
+          <t>Apskritos arba kampuotos standaus skerspjūvio formos komponentas, uždaroje aplinkoje nukreipiantis oro ir (arba) dujų srautą.</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
-      <c r="J30" s="7" t="n"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>IfcDuctSegment, 
+IfcDuctSegmentType</t>
+        </is>
+      </c>
       <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="9" t="n"/>
-      <c r="S30" s="9" t="n"/>
-      <c r="T30" s="10" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="31" outlineLevel="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="T31" s="12" t="n"/>
+      <c r="A31" s="12" t="n"/>
+      <c r="T31" s="14" t="n"/>
     </row>
     <row r="32" outlineLevel="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Srauto šakotuvas</t>
+          <t>Išardoma jungtis</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1518,46 +1563,55 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XMA</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Šakotuvas</t>
+          <t>Išardoma jungtis</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Fluido srautą skirstanti ir (ar) jungianti jungtis.</t>
+          <t>Išardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
-      <c r="J32" s="7" t="n"/>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
+        </is>
+      </c>
       <c r="K32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9" t="n"/>
-      <c r="O32" s="9" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="9" t="n"/>
-      <c r="S32" s="9" t="n"/>
-      <c r="T32" s="10" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="33" outlineLevel="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="T33" s="12" t="n"/>
+      <c r="A33" s="12" t="n"/>
+      <c r="T33" s="14" t="n"/>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ventiliatorius</t>
+          <t>Neišardoma jungtis</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1572,46 +1626,55 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>GQB</t>
+          <t>XMB</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Ventiliatorius</t>
+          <t>Neišardoma jungtis</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Oro srautą sukuriantis komponentas.</t>
+          <t>Neišardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
-      <c r="J34" s="7" t="n"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
+        </is>
+      </c>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="9" t="n"/>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="9" t="n"/>
-      <c r="S34" s="9" t="n"/>
-      <c r="T34" s="10" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="n"/>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="35" outlineLevel="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="T35" s="12" t="n"/>
+      <c r="A35" s="12" t="n"/>
+      <c r="T35" s="14" t="n"/>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Apsaugos priedanga</t>
+          <t>Kampinė jungtis</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1626,131 +1689,170 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>XMD</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Stogelis</t>
+          <t>Kampinė jungtis</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Komponentas, apsaugantis nuo įvairių klimato sukeliamų poveikių.</t>
+          <t>Komponentas, skirtas sujungti ir pakeisti fluido srauto kryptį.</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
-      <c r="J36" s="7" t="n"/>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
+        </is>
+      </c>
       <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
-      <c r="O36" s="9" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="9" t="n"/>
-      <c r="S36" s="9" t="n"/>
-      <c r="T36" s="10" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="37" outlineLevel="1">
-      <c r="A37" s="11" t="n"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>Pset_ConstructionAdministration.SpecificationSectionNumber</t>
-        </is>
-      </c>
-      <c r="N37" s="13" t="inlineStr">
-        <is>
-          <t>A reference number to an external contract technical specification section describing either (a) minimum performance requirements of a given IfcProductType/[[IfcProduct]] or (b) a preselection for a specific IfcProductType/[[IfcProduct]] made for this project.</t>
-        </is>
-      </c>
-      <c r="P37" s="13" t="inlineStr">
+      <c r="A37" s="12" t="n"/>
+      <c r="T37" s="14" t="n"/>
+    </row>
+    <row r="38" outlineLevel="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Grotelės</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>NAC</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Grotelės</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Užpildantis komponentas, praleidžiantis skysčius.</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1">
+      <c r="A39" s="12" t="n"/>
+      <c r="M39" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="T37" s="12" t="n"/>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="11" t="n"/>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>Pset_ElementCommon.System</t>
-        </is>
-      </c>
-      <c r="N38" s="13" t="inlineStr">
-        <is>
-          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
-        </is>
-      </c>
-      <c r="P38" s="13" t="inlineStr">
+      <c r="T39" s="14" t="n"/>
+    </row>
+    <row r="40" outlineLevel="1">
+      <c r="A40" s="12" t="n"/>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N40" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="T38" s="12" t="n"/>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="11" t="n"/>
-      <c r="M39" s="13" t="inlineStr">
-        <is>
-          <t>Pset_ElementComponentCommon.Status</t>
-        </is>
-      </c>
-      <c r="N39" s="13" t="inlineStr">
-        <is>
-          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
-        </is>
-      </c>
-      <c r="P39" s="13" t="inlineStr">
+      <c r="T40" s="14" t="n"/>
+    </row>
+    <row r="41" outlineLevel="1">
+      <c r="A41" s="12" t="n"/>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P41" s="13" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="T39" s="12" t="n"/>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="A40" s="11" t="n"/>
-      <c r="M40" s="13" t="inlineStr">
-        <is>
-          <t>VVK.ElementType</t>
-        </is>
-      </c>
-      <c r="N40" s="13" t="inlineStr">
-        <is>
-          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
-        </is>
-      </c>
-      <c r="P40" s="13" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="T40" s="12" t="n"/>
-    </row>
-    <row r="41" outlineLevel="1">
-      <c r="A41" s="11" t="n"/>
-      <c r="M41" s="13" t="inlineStr">
-        <is>
-          <t>VVK.Name</t>
-        </is>
-      </c>
-      <c r="T41" s="12" t="n"/>
+      <c r="T41" s="14" t="n"/>
     </row>
     <row r="42" outlineLevel="1">
-      <c r="A42" s="11" t="n"/>
-      <c r="T42" s="12" t="n"/>
+      <c r="A42" s="12" t="n"/>
+      <c r="T42" s="14" t="n"/>
     </row>
     <row r="43" outlineLevel="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Atskirtuvas</t>
+          <t>Difuzorius</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1765,48 +1867,52 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>HQB</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Filtras</t>
+          <t>Difuzorius</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Mechaninio atskyrimo komponentas, atskiriantis daleles atsižvelgiant į jų dydį ar formą.</t>
+          <t>Srauto ribotuvas, fiksuotomis priemonėmis apribojantis ir formuojantis srautą.</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="9" t="n"/>
-      <c r="O43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
-      <c r="T43" s="10" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1">
-      <c r="A44" s="11" t="n"/>
+      <c r="A44" s="12" t="n"/>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>Pset_ConstructionAdministration.SpecificationSectionNumber</t>
+          <t>Pset_ElementComponentCommon.Status</t>
         </is>
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
-          <t>A reference number to an external contract technical specification section describing either (a) minimum performance requirements of a given IfcProductType/[[IfcProduct]] or (b) a preselection for a specific IfcProductType/[[IfcProduct]] made for this project.</t>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
         </is>
       </c>
       <c r="P44" s="13" t="inlineStr">
@@ -1814,18 +1920,18 @@
           <t>String</t>
         </is>
       </c>
-      <c r="T44" s="12" t="n"/>
+      <c r="T44" s="14" t="n"/>
     </row>
     <row r="45" outlineLevel="1">
-      <c r="A45" s="11" t="n"/>
+      <c r="A45" s="12" t="n"/>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>Pset_ElementCommon.System</t>
+          <t>VVK.ElementType</t>
         </is>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
-          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -1833,678 +1939,1365 @@
           <t>String</t>
         </is>
       </c>
-      <c r="T45" s="12" t="n"/>
+      <c r="T45" s="14" t="n"/>
     </row>
     <row r="46" outlineLevel="1">
-      <c r="A46" s="11" t="n"/>
+      <c r="A46" s="12" t="n"/>
       <c r="M46" s="13" t="inlineStr">
         <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N46" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P46" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T46" s="14" t="n"/>
+    </row>
+    <row r="47" outlineLevel="1">
+      <c r="A47" s="12" t="n"/>
+      <c r="T47" s="14" t="n"/>
+    </row>
+    <row r="48" outlineLevel="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Oro skirstytuvas</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>%RND10</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>Oro skirstytuvas</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Oro srautą formuojantis, praleidžiantis ir maišantis įrenginys.</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1">
+      <c r="A49" s="12" t="n"/>
+      <c r="M49" s="13" t="inlineStr">
+        <is>
           <t>Pset_ElementComponentCommon.Status</t>
         </is>
       </c>
-      <c r="N46" s="13" t="inlineStr">
+      <c r="N49" s="13" t="inlineStr">
         <is>
           <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
         </is>
       </c>
-      <c r="P46" s="13" t="inlineStr">
+      <c r="P49" s="13" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="T46" s="12" t="n"/>
-    </row>
-    <row r="47" outlineLevel="1">
-      <c r="A47" s="11" t="n"/>
-      <c r="M47" s="13" t="inlineStr">
+      <c r="T49" s="14" t="n"/>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="A50" s="12" t="n"/>
+      <c r="M50" s="13" t="inlineStr">
         <is>
           <t>VVK.ElementType</t>
         </is>
       </c>
-      <c r="N47" s="13" t="inlineStr">
+      <c r="N50" s="13" t="inlineStr">
         <is>
           <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
         </is>
       </c>
-      <c r="P47" s="13" t="inlineStr">
+      <c r="P50" s="13" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="T47" s="12" t="n"/>
-    </row>
-    <row r="48" outlineLevel="1">
-      <c r="A48" s="11" t="n"/>
-      <c r="M48" s="13" t="inlineStr">
+      <c r="T50" s="14" t="n"/>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="A51" s="12" t="n"/>
+      <c r="M51" s="13" t="inlineStr">
         <is>
           <t>VVK.Name</t>
         </is>
       </c>
-      <c r="T48" s="12" t="n"/>
-    </row>
-    <row r="49" outlineLevel="1">
-      <c r="A49" s="11" t="n"/>
-      <c r="T49" s="12" t="n"/>
-    </row>
-    <row r="50" outlineLevel="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Dujų uždarymo komponentas</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P51" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T51" s="14" t="n"/>
+    </row>
+    <row r="52" outlineLevel="1">
+      <c r="A52" s="12" t="n"/>
+      <c r="T52" s="14" t="n"/>
+    </row>
+    <row r="53" outlineLevel="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Dujų reguliavimo vožtuvas</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>QMB</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>Dujų sklendė</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>Sandarių dujų (oro) sistemų perjungimo komponentas dujų srautui valdyti.</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>QNB</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Reguliavimo sklendė</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Komponentas, sandariose skysčio sistemose reguliuojantis dujų srautą.</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>IfcValve, 
+IfcValveType, 
+IfcValveTypeEnum</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="A54" s="12" t="n"/>
+      <c r="T54" s="14" t="n"/>
+    </row>
+    <row r="55" outlineLevel="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Srauto šakotuvas</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>Šakotuvas</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Fluido srautą skirstanti ir (ar) jungianti jungtis.</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="12" t="n"/>
+      <c r="T56" s="14" t="n"/>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Ventiliatorius</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>GQB</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Ventiliatorius</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Oro srautą sukuriantis komponentas.</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="12" t="n"/>
+      <c r="T58" s="14" t="n"/>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Apsaugos priedanga</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>FSD</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Stogelis</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Komponentas, apsaugantis nuo įvairių klimato sukeliamų poveikių.</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="12" t="n"/>
+      <c r="M60" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N60" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P60" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T60" s="14" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="12" t="n"/>
+      <c r="M61" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Thickness</t>
+        </is>
+      </c>
+      <c r="N61" s="13" t="inlineStr">
+        <is>
+          <t>The geometric thickness of the object.</t>
+        </is>
+      </c>
+      <c r="P61" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T61" s="14" t="n"/>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="12" t="n"/>
+      <c r="M62" s="13" t="inlineStr">
+        <is>
+          <t>Pset_QuantityTakeOff.Area</t>
+        </is>
+      </c>
+      <c r="N62" s="13" t="inlineStr">
+        <is>
+          <t>Calculated area for the object.</t>
+        </is>
+      </c>
+      <c r="P62" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T62" s="14" t="n"/>
+    </row>
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="12" t="n"/>
+      <c r="M63" s="13" t="inlineStr">
+        <is>
+          <t>Pset_QuantityTakeOff.Volume</t>
+        </is>
+      </c>
+      <c r="T63" s="14" t="n"/>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" s="12" t="n"/>
+      <c r="M64" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N64" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P64" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T64" s="14" t="n"/>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="12" t="n"/>
+      <c r="M65" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N65" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P65" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T65" s="14" t="n"/>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="A66" s="12" t="n"/>
+      <c r="T66" s="14" t="n"/>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Atskirtuvas</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>HQB</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>Filtras</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Mechaninio atskyrimo komponentas, atskiriantis daleles atsižvelgiant į jų dydį ar formą.</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K50" s="7" t="n"/>
-      <c r="L50" s="7" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
-      <c r="O50" s="9" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
-      <c r="R50" s="9" t="n"/>
-      <c r="S50" s="9" t="n"/>
-      <c r="T50" s="10" t="inlineStr">
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="51" outlineLevel="1">
-      <c r="A51" s="11" t="n"/>
-      <c r="T51" s="12" t="n"/>
-    </row>
-    <row r="52" outlineLevel="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="68" outlineLevel="1">
+      <c r="A68" s="12" t="n"/>
+      <c r="T68" s="14" t="n"/>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Dujų uždarymo komponentas</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>QMB</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>Dujų sklendė</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Sandarių dujų (oro) sistemų perjungimo komponentas dujų srautui valdyti.</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>IfcValve, 
+IfcValveType, 
+IfcValveTypeEnum</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="12" t="n"/>
+      <c r="T70" s="14" t="n"/>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Elektrinis karšto oro pūstuvas</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>EBD</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Karšto oro pūstuvas</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Elektrinis šildytuvas, perduodantis šilumą priverstinio oro srautu.</t>
         </is>
       </c>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="7" t="n"/>
-      <c r="K52" s="7" t="n"/>
-      <c r="L52" s="7" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="10" t="inlineStr">
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>IfcHeatExchanger, 
+IfcHeatExchangerType, 
+IfcHeatExchangerTypeEnum, 
+IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="53" outlineLevel="1">
-      <c r="A53" s="11" t="n"/>
-      <c r="T53" s="12" t="n"/>
-    </row>
-    <row r="54" outlineLevel="1">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="72" outlineLevel="1">
+      <c r="A72" s="12" t="n"/>
+      <c r="T72" s="14" t="n"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Karšto ir (arba) vėsaus oro pūstuvas</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>EPD</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Karšto ir (arba) vėsaus oro pūstuvas</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Šildymo ir (arba) vėsinimo įrenginys, perduodantis energiją oro srautu.</t>
         </is>
       </c>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="7" t="n"/>
-      <c r="K54" s="7" t="n"/>
-      <c r="L54" s="7" t="n"/>
-      <c r="M54" s="9" t="n"/>
-      <c r="N54" s="9" t="n"/>
-      <c r="O54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
-      <c r="R54" s="9" t="n"/>
-      <c r="S54" s="9" t="n"/>
-      <c r="T54" s="10" t="inlineStr">
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>IfcHeatExchanger, 
+IfcHeatExchangerType, 
+IfcHeatExchangerTypeEnum, 
+IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="55" outlineLevel="1">
-      <c r="A55" s="11" t="n"/>
-      <c r="T55" s="12" t="n"/>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="12" t="n"/>
+      <c r="T74" s="14" t="n"/>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Triukšmo slopinimo komponentas</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>RQC</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Triukšmo slopinimo komponentas</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Vietinį klimatą reguliuojantis komponentas, skirtas slopinti ir nukreipti triukšmą.</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="7" t="n"/>
-      <c r="K56" s="7" t="n"/>
-      <c r="L56" s="7" t="n"/>
-      <c r="M56" s="9" t="n"/>
-      <c r="N56" s="9" t="n"/>
-      <c r="O56" s="9" t="n"/>
-      <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
-      <c r="R56" s="9" t="n"/>
-      <c r="S56" s="9" t="n"/>
-      <c r="T56" s="10" t="inlineStr">
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>IfcValve, 
+IfcValveType, 
+IfcValveTypeEnum</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
-      <c r="A57" s="11" t="n"/>
-      <c r="T57" s="12" t="n"/>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="12" t="n"/>
+      <c r="T76" s="14" t="n"/>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Daugiaparametris jutiklis</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>BUA</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Daugiaparametris jutiklis</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Daugiaparametris jutimo komponentas su skaliariniu išėjimu.</t>
         </is>
       </c>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="7" t="n"/>
-      <c r="K58" s="7" t="n"/>
-      <c r="L58" s="7" t="n"/>
-      <c r="M58" s="9" t="n"/>
-      <c r="N58" s="9" t="n"/>
-      <c r="O58" s="9" t="n"/>
-      <c r="P58" s="9" t="n"/>
-      <c r="Q58" s="9" t="n"/>
-      <c r="R58" s="9" t="n"/>
-      <c r="S58" s="9" t="n"/>
-      <c r="T58" s="10" t="inlineStr">
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="11" t="inlineStr">
         <is>
           <t>ŠVOK.V</t>
         </is>
       </c>
     </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="11" t="n"/>
-      <c r="T59" s="12" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="n"/>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="15" t="n"/>
-      <c r="D60" s="15" t="n"/>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="15" t="n"/>
-      <c r="J60" s="15" t="n"/>
-      <c r="K60" s="15" t="n"/>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="n"/>
-      <c r="N60" s="15" t="n"/>
-      <c r="O60" s="15" t="n"/>
-      <c r="P60" s="15" t="n"/>
-      <c r="Q60" s="15" t="n"/>
-      <c r="R60" s="15" t="n"/>
-      <c r="S60" s="15" t="n"/>
-      <c r="T60" s="16" t="n"/>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="12" t="n"/>
+      <c r="T78" s="14" t="n"/>
+    </row>
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>%DCB1000</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Vėdinimo įrenginių aptarnavimo erdvė</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>IfcSpace, 
+IfcSpaceType</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="11" t="inlineStr">
+        <is>
+          <t>ŠVOK.V</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" outlineLevel="1">
+      <c r="A80" s="12" t="n"/>
+      <c r="M80" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N80" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P80" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T80" s="14" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="12" t="n"/>
+      <c r="M81" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N81" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P81" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T81" s="14" t="n"/>
+    </row>
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="12" t="n"/>
+      <c r="T82" s="14" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="17" t="n"/>
+      <c r="C83" s="17" t="n"/>
+      <c r="D83" s="17" t="n"/>
+      <c r="E83" s="17" t="n"/>
+      <c r="F83" s="17" t="n"/>
+      <c r="G83" s="17" t="n"/>
+      <c r="H83" s="17" t="n"/>
+      <c r="I83" s="17" t="n"/>
+      <c r="J83" s="17" t="n"/>
+      <c r="K83" s="17" t="n"/>
+      <c r="L83" s="17" t="n"/>
+      <c r="M83" s="17" t="n"/>
+      <c r="N83" s="17" t="n"/>
+      <c r="O83" s="17" t="n"/>
+      <c r="P83" s="17" t="n"/>
+      <c r="Q83" s="17" t="n"/>
+      <c r="R83" s="17" t="n"/>
+      <c r="S83" s="17" t="n"/>
+      <c r="T83" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="309">
+  <mergeCells count="335">
     <mergeCell ref="I32:I33"/>
     <mergeCell ref="K32:K33"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="C36:C42"/>
-    <mergeCell ref="T50:T51"/>
-    <mergeCell ref="E36:E42"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G59:G66"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="L55:L56"/>
+    <mergeCell ref="T73:T74"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="F15:F21"/>
+    <mergeCell ref="F22:F29"/>
+    <mergeCell ref="H22:H29"/>
+    <mergeCell ref="K53:K54"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="J73:J74"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="L38:L42"/>
+    <mergeCell ref="J77:J78"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="F38:F42"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="K71:K72"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="T69:T70"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="A48:A52"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B43:B49"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D36:D42"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="F36:F42"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="T71:T72"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="C36:C37"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="L26:L27"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="K73:K74"/>
+    <mergeCell ref="T38:T42"/>
+    <mergeCell ref="T77:T78"/>
+    <mergeCell ref="L77:L78"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="E38:E42"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="G38:G42"/>
     <mergeCell ref="E34:E35"/>
+    <mergeCell ref="H73:H74"/>
     <mergeCell ref="G34:G35"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="T26:T27"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="K67:K68"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="H4:H6"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A43:A49"/>
     <mergeCell ref="H32:H33"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="T52:T53"/>
-    <mergeCell ref="T24:T25"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L75:L76"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="C79:C82"/>
+    <mergeCell ref="E79:E82"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="K48:K52"/>
+    <mergeCell ref="C48:C52"/>
+    <mergeCell ref="K77:K78"/>
+    <mergeCell ref="A15:A21"/>
     <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J43:J49"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C29"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="C57:C58"/>
     <mergeCell ref="L1:S1"/>
-    <mergeCell ref="L36:L42"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="T75:T76"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="B79:B82"/>
+    <mergeCell ref="D79:D82"/>
     <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F34:F35"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="I43:I49"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="K43:K49"/>
+    <mergeCell ref="F36:F37"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="T55:T56"/>
+    <mergeCell ref="B69:B70"/>
     <mergeCell ref="L34:L35"/>
-    <mergeCell ref="A36:A42"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="C43:C49"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="H43:H49"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="C59:C66"/>
+    <mergeCell ref="C15:C21"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="D48:D52"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="B15:B21"/>
+    <mergeCell ref="B22:B29"/>
+    <mergeCell ref="D15:D21"/>
+    <mergeCell ref="D22:D29"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="E59:E66"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="J67:J68"/>
+    <mergeCell ref="T67:T68"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
     <mergeCell ref="F32:F33"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="B36:B42"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="B59:B66"/>
+    <mergeCell ref="J79:J82"/>
+    <mergeCell ref="L79:L82"/>
+    <mergeCell ref="J48:J52"/>
+    <mergeCell ref="T48:T52"/>
+    <mergeCell ref="L48:L52"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="J22:J29"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="L67:L68"/>
+    <mergeCell ref="A22:A29"/>
     <mergeCell ref="A30:A31"/>
-    <mergeCell ref="T10:T11"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F53:F54"/>
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="K79:K82"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D59:D66"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="I38:I42"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="K38:K42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="C38:C42"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="T36:T42"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="J15:J21"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="L15:L21"/>
+    <mergeCell ref="L22:L29"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="T43:T49"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="L59:L66"/>
+    <mergeCell ref="L57:L58"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="I22:I29"/>
+    <mergeCell ref="K15:K21"/>
+    <mergeCell ref="K22:K29"/>
+    <mergeCell ref="K57:K58"/>
     <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="H14:H15"/>
     <mergeCell ref="D30:D31"/>
-    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H36:H42"/>
-    <mergeCell ref="J36:J42"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="J59:J66"/>
+    <mergeCell ref="F48:F52"/>
+    <mergeCell ref="H48:H52"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="T15:T21"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E43:E49"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="G43:G49"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="H43:H47"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="K59:K66"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="G36:G42"/>
-    <mergeCell ref="I36:I42"/>
-    <mergeCell ref="K36:K42"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="A59:A66"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="C75:C76"/>
     <mergeCell ref="J30:J31"/>
+    <mergeCell ref="B4:B6"/>
     <mergeCell ref="L30:L31"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L73:L74"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="T59:T66"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="J38:J42"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="H77:H78"/>
     <mergeCell ref="G32:G33"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="T36:T37"/>
+    <mergeCell ref="I59:I66"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="H34:H35"/>
-    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="K4:K6"/>
     <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D43:D49"/>
-    <mergeCell ref="F43:F49"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="T56:T57"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="T79:T82"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="T22:T29"/>
+    <mergeCell ref="G36:G37"/>
     <mergeCell ref="I30:I31"/>
     <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E55:E56"/>
     <mergeCell ref="J34:J35"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="T43:T47"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="H75:H76"/>
     <mergeCell ref="I34:I35"/>
+    <mergeCell ref="F11:F12"/>
     <mergeCell ref="K34:K35"/>
-    <mergeCell ref="K28:K29"/>
     <mergeCell ref="T32:T33"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="T28:T29"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="J4:J6"/>
     <mergeCell ref="T30:T31"/>
+    <mergeCell ref="T57:T58"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="B71:B72"/>
     <mergeCell ref="L32:L33"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="T58:T59"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="L50:L51"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="D38:D42"/>
+    <mergeCell ref="F59:F66"/>
+    <mergeCell ref="H59:H66"/>
+    <mergeCell ref="H15:H21"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="J75:J76"/>
     <mergeCell ref="T34:T35"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="L52:L53"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="L43:L49"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="I79:I82"/>
+    <mergeCell ref="E48:E52"/>
+    <mergeCell ref="G48:G52"/>
+    <mergeCell ref="E15:E21"/>
+    <mergeCell ref="E22:E29"/>
+    <mergeCell ref="G15:G21"/>
+    <mergeCell ref="G22:G29"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="T53:T54"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F79:F82"/>
+    <mergeCell ref="H79:H82"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="T4:T6"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="A73:A74"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
